--- a/data/trans_orig/P33_2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana</t>
+          <t>Número medio de horas que duerme habitualmente al día durante los fines de semana (tasa de respuesta: 97,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,29</t>
+          <t>7,15; 7,28</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,93</t>
+          <t>7,42; 9,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,36</t>
+          <t>7,21; 7,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,53</t>
+          <t>7,35; 8,48</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 7,35</t>
+          <t>6,53; 7,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,39</t>
+          <t>6,77; 7,4</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,41</t>
+          <t>7,21; 7,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,36</t>
+          <t>7,23; 7,35</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,08</t>
+          <t>7,36; 8,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,26</t>
+          <t>6,99; 7,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,67</t>
+          <t>7,24; 7,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33_2_2023-Habitat-trans_orig.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>7,21</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,46</t>
+          <t>7,26; 7,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,15</t>
+          <t>7,0; 7,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,28</t>
+          <t>7,15; 7,27</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>7,3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>7,37</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,09</t>
+          <t>7,37; 7,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,35</t>
+          <t>7,23; 7,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,48</t>
+          <t>7,32; 7,42</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,42</t>
+          <t>7,43</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,19</t>
+          <t>7,38</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,54</t>
+          <t>7,33; 7,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,35</t>
+          <t>7,24; 7,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,4</t>
+          <t>7,31; 7,45</t>
         </is>
       </c>
     </row>
@@ -703,12 +703,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>7,28</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,29</t>
+          <t>7,3</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,41</t>
+          <t>7,22; 7,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,38</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 8,13</t>
+          <t>7,34; 7,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,26</t>
+          <t>7,22; 7,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,72</t>
+          <t>7,29; 7,35</t>
         </is>
       </c>
     </row>
